--- a/Banco ITESIANO.xlsx
+++ b/Banco ITESIANO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/106876cc2438bd37/Desktop/TRABAJO/UNI/8VO SEMESTRE/ADMINISTRACION_RIESGOS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Desktop\TRABAJO\UNI\8VO SEMESTRE\ADMINISTRACION_RIESGOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{3AFDB6EA-5B37-42E8-B61A-5E9AFF02BDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8E225F3-218F-4F3B-A178-F0144BE69011}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D14C082-0708-408A-908D-A374F05187A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23114C35-11CD-4BE2-8A9D-20C25953A90A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{23114C35-11CD-4BE2-8A9D-20C25953A90A}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -390,11 +390,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -846,42 +845,42 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{65C90BFE-C9E6-4D8B-B6A4-5295C361B441}">
   <dimension ref="A1:H81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.44140625" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
+    <col min="1" max="1" width="5.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="5"/>
-      <c r="C2" s="5" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="4"/>
+      <c r="C2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -904,7 +903,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -927,7 +926,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
         <v>8</v>
       </c>
@@ -956,7 +955,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
         <v>9</v>
       </c>
@@ -972,7 +971,7 @@
         <f t="shared" ref="E6:H6" si="1">E5+D6</f>
         <v>-530</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="3">
         <f t="shared" si="1"/>
         <v>-560</v>
       </c>
@@ -985,49 +984,49 @@
         <v>-140</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B19" s="7" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F19" s="7" t="s">
+      <c r="F19" s="6" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>15</v>
       </c>
@@ -1037,7 +1036,7 @@
       <c r="D20" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="5">
         <v>0</v>
       </c>
       <c r="F20">
@@ -1045,7 +1044,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>21</v>
       </c>
@@ -1055,7 +1054,7 @@
       <c r="D21" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="5">
         <v>0</v>
       </c>
       <c r="F21">
@@ -1063,7 +1062,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" t="s">
         <v>22</v>
       </c>
@@ -1073,7 +1072,7 @@
       <c r="D22" t="s">
         <v>24</v>
       </c>
-      <c r="E22" s="6">
+      <c r="E22" s="5">
         <v>0.15</v>
       </c>
       <c r="F22">
@@ -1081,30 +1080,30 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="23" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F23" s="8">
+      <c r="F23" s="7">
         <f>SUM(F20:F22)</f>
         <v>727.5</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="B25" s="9" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B25" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="D25" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="E25" s="9" t="s">
+      <c r="E25" s="8" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
         <v>27</v>
       </c>
@@ -1119,7 +1118,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
         <v>28</v>
       </c>
@@ -1134,7 +1133,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>29</v>
       </c>
@@ -1149,7 +1148,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="29" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
         <v>30</v>
       </c>
@@ -1164,64 +1163,64 @@
         <v>210</v>
       </c>
     </row>
-    <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="7">
         <f>SUM(E26:E29)</f>
         <v>489</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="9">
         <f>F23/E30</f>
         <v>1.4877300613496933</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B43" s="13" t="s">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="13" t="s">
+      <c r="E43" s="12" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B44" s="12" t="s">
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-    </row>
-    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>41</v>
       </c>
       <c r="C45">
         <v>980</v>
       </c>
-      <c r="D45" s="11">
+      <c r="D45" s="10">
         <v>1</v>
       </c>
       <c r="E45">
@@ -1229,14 +1228,14 @@
         <v>980</v>
       </c>
     </row>
-    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>42</v>
       </c>
       <c r="C46">
         <v>320</v>
       </c>
-      <c r="D46" s="11">
+      <c r="D46" s="10">
         <v>1</v>
       </c>
       <c r="E46">
@@ -1244,14 +1243,14 @@
         <v>320</v>
       </c>
     </row>
-    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
         <v>43</v>
       </c>
       <c r="C47">
         <v>680</v>
       </c>
-      <c r="D47" s="11">
+      <c r="D47" s="10">
         <v>0.95</v>
       </c>
       <c r="E47">
@@ -1259,14 +1258,14 @@
         <v>646</v>
       </c>
     </row>
-    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" t="s">
         <v>44</v>
       </c>
       <c r="C48">
         <v>120</v>
       </c>
-      <c r="D48" s="11">
+      <c r="D48" s="10">
         <v>0.9</v>
       </c>
       <c r="E48">
@@ -1274,14 +1273,14 @@
         <v>108</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
         <v>45</v>
       </c>
       <c r="C49">
         <v>180</v>
       </c>
-      <c r="D49" s="11">
+      <c r="D49" s="10">
         <v>0.5</v>
       </c>
       <c r="E49">
@@ -1289,31 +1288,31 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B50" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="7">
         <f>SUM(E45:E49)</f>
         <v>2144</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B52" s="12" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B52" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>48</v>
       </c>
       <c r="C53">
         <v>320</v>
       </c>
-      <c r="D53" s="11">
+      <c r="D53" s="10">
         <v>0</v>
       </c>
       <c r="E53">
@@ -1321,14 +1320,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>49</v>
       </c>
       <c r="C54">
         <v>280</v>
       </c>
-      <c r="D54" s="11">
+      <c r="D54" s="10">
         <v>0.05</v>
       </c>
       <c r="E54">
@@ -1336,14 +1335,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>50</v>
       </c>
       <c r="C55">
         <v>150</v>
       </c>
-      <c r="D55" s="11">
+      <c r="D55" s="10">
         <v>0.15</v>
       </c>
       <c r="E55">
@@ -1351,14 +1350,14 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B56" t="s">
         <v>51</v>
       </c>
       <c r="C56">
         <v>420</v>
       </c>
-      <c r="D56" s="11">
+      <c r="D56" s="10">
         <v>0.5</v>
       </c>
       <c r="E56">
@@ -1366,14 +1365,14 @@
         <v>210</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>52</v>
       </c>
       <c r="C57">
         <v>1850</v>
       </c>
-      <c r="D57" s="11">
+      <c r="D57" s="10">
         <v>0.85</v>
       </c>
       <c r="E57">
@@ -1381,14 +1380,14 @@
         <v>1572.5</v>
       </c>
     </row>
-    <row r="58" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B58" t="s">
         <v>53</v>
       </c>
       <c r="C58">
         <v>180</v>
       </c>
-      <c r="D58" s="11">
+      <c r="D58" s="10">
         <v>1</v>
       </c>
       <c r="E58">
@@ -1396,25 +1395,25 @@
         <v>180</v>
       </c>
     </row>
-    <row r="59" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B59" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E59" s="8">
+      <c r="E59" s="7">
         <f>SUM(E53:E58)</f>
         <v>1999</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C61" s="10">
+      <c r="C61" s="9">
         <f>E50/E59</f>
         <v>1.0725362681340671</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>58</v>
       </c>
@@ -1422,75 +1421,75 @@
         <v>59</v>
       </c>
     </row>
-    <row r="65" spans="1:4" ht="25.8" x14ac:dyDescent="0.5">
-      <c r="A65" s="14" t="s">
+    <row r="65" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
+      <c r="A65" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B65" s="15"/>
-      <c r="C65" s="15"/>
-      <c r="D65" s="15"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B68" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B70" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B71" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B72" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B75" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B76" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B79" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B80" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="81" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B81" t="s">
         <v>73</v>
       </c>
